--- a/notebooks/experimental_results/sucessDFDarks.xlsx
+++ b/notebooks/experimental_results/sucessDFDarks.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdreiling/Desktop/puck/puck/notebooks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jdreiling/Desktop/puck/puck/notebooks/experimental_results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{82345499-C45C-5345-ACE4-544CC466C5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859006C2-813C-2B48-BA38-AD4CCAC01BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1200" yWindow="1720" windowWidth="27240" windowHeight="16180" xr2:uid="{925124AB-CAC5-6049-BBA0-FB3175284F09}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -2821,13 +2821,13 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:XFD4 A6:XFD34 A36:XFD1048576 A35:B35 D35:XFD35">
+  <conditionalFormatting sqref="A1:XFD4">
     <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C35">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="A6:XFD1048576">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3812,7 +3812,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4932,13 +4932,13 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="K6">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="A1:XFD1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+  <conditionalFormatting sqref="K6">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
